--- a/Poten/Poten_West_Positions_All_Emails.xlsx
+++ b/Poten/Poten_West_Positions_All_Emails.xlsx
@@ -316,7 +316,7 @@
     <t>Poten</t>
   </si>
   <si>
-    <t>2026-02-27 16:01:16</t>
+    <t>2026-02-26</t>
   </si>
   <si>
     <t>C:\Users\THADLOW\OneDrive - Axpo Services AG\Desktop\SHIPPING BROKER REPORTS\Poten\Emails\2026-02-27_160119__FW_ Poten &amp; Partners Daily Shipping Report_ 26.02.2026\2026-02-27_160119__FW_ Poten &amp; Partners Daily Shipping Report_ 26.02.2026.msg</t>
